--- a/research/traditional_assets/database/data/new_zealand/new_zealand_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="E2">
-        <v>0.09949999999999999</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="F2">
-        <v>0.03759999999999999</v>
+        <v>0.0429</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>60.8</v>
+        <v>59.2</v>
       </c>
       <c r="L2">
-        <v>0.3687083080654942</v>
+        <v>0.3749208359721343</v>
       </c>
       <c r="M2">
-        <v>21.2</v>
+        <v>36.1</v>
       </c>
       <c r="N2">
-        <v>0.02084152575697994</v>
+        <v>0.0448558648111332</v>
       </c>
       <c r="O2">
-        <v>0.3486842105263158</v>
+        <v>0.6097972972972973</v>
       </c>
       <c r="P2">
-        <v>21.2</v>
+        <v>36.1</v>
       </c>
       <c r="Q2">
-        <v>0.02084152575697994</v>
+        <v>0.0448558648111332</v>
       </c>
       <c r="R2">
-        <v>0.3486842105263158</v>
+        <v>0.6097972972972973</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>121</v>
+        <v>180.8</v>
       </c>
       <c r="V2">
-        <v>0.1189539913488006</v>
+        <v>0.2246520874751491</v>
       </c>
       <c r="W2">
-        <v>0.1345430404956849</v>
+        <v>0.111320045129748</v>
       </c>
       <c r="X2">
-        <v>0.05857585721580783</v>
+        <v>0.1029808301471179</v>
       </c>
       <c r="Y2">
-        <v>0.07596718327987706</v>
+        <v>0.008339214982630141</v>
       </c>
       <c r="Z2">
-        <v>0.1404480027254919</v>
+        <v>0.1009074642126789</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03609691283998011</v>
+        <v>0.05694561925493129</v>
       </c>
       <c r="AC2">
-        <v>-0.03609691283998011</v>
+        <v>-0.05694561925493129</v>
       </c>
       <c r="AD2">
-        <v>1185.5</v>
+        <v>1618.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1185.5</v>
+        <v>1618.6</v>
       </c>
       <c r="AG2">
-        <v>1064.5</v>
+        <v>1437.8</v>
       </c>
       <c r="AH2">
-        <v>0.5382031143596495</v>
+        <v>0.6679045968474046</v>
       </c>
       <c r="AI2">
-        <v>0.6903278402142899</v>
+        <v>0.7628069183279136</v>
       </c>
       <c r="AJ2">
-        <v>0.5113609069510496</v>
+        <v>0.6411308302862748</v>
       </c>
       <c r="AK2">
-        <v>0.6668546012654263</v>
+        <v>0.7407140281283808</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="E3">
-        <v>0.09949999999999999</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="F3">
-        <v>0.03759999999999999</v>
+        <v>0.0429</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>60.8</v>
+        <v>59.2</v>
       </c>
       <c r="L3">
-        <v>0.3687083080654942</v>
+        <v>0.3749208359721343</v>
       </c>
       <c r="M3">
-        <v>21.2</v>
+        <v>36.1</v>
       </c>
       <c r="N3">
-        <v>0.02084152575697994</v>
+        <v>0.0448558648111332</v>
       </c>
       <c r="O3">
-        <v>0.3486842105263158</v>
+        <v>0.6097972972972973</v>
       </c>
       <c r="P3">
-        <v>21.2</v>
+        <v>36.1</v>
       </c>
       <c r="Q3">
-        <v>0.02084152575697994</v>
+        <v>0.0448558648111332</v>
       </c>
       <c r="R3">
-        <v>0.3486842105263158</v>
+        <v>0.6097972972972973</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>121</v>
+        <v>180.8</v>
       </c>
       <c r="V3">
-        <v>0.1189539913488006</v>
+        <v>0.2246520874751491</v>
       </c>
       <c r="W3">
-        <v>0.1345430404956849</v>
+        <v>0.111320045129748</v>
       </c>
       <c r="X3">
-        <v>0.05857585721580783</v>
+        <v>0.1029808301471179</v>
       </c>
       <c r="Y3">
-        <v>0.07596718327987706</v>
+        <v>0.008339214982630141</v>
       </c>
       <c r="Z3">
-        <v>0.1404480027254919</v>
+        <v>0.1009074642126789</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03609691283998011</v>
+        <v>0.05694561925493129</v>
       </c>
       <c r="AC3">
-        <v>-0.03609691283998011</v>
+        <v>-0.05694561925493129</v>
       </c>
       <c r="AD3">
-        <v>1185.5</v>
+        <v>1618.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1185.5</v>
+        <v>1618.6</v>
       </c>
       <c r="AG3">
-        <v>1064.5</v>
+        <v>1437.8</v>
       </c>
       <c r="AH3">
-        <v>0.5382031143596495</v>
+        <v>0.6679045968474046</v>
       </c>
       <c r="AI3">
-        <v>0.6903278402142899</v>
+        <v>0.7628069183279136</v>
       </c>
       <c r="AJ3">
-        <v>0.5113609069510496</v>
+        <v>0.6411308302862748</v>
       </c>
       <c r="AK3">
-        <v>0.6668546012654263</v>
+        <v>0.7407140281283808</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.102</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="E2">
-        <v>0.09359999999999999</v>
+        <v>0.0727</v>
       </c>
       <c r="F2">
-        <v>0.0429</v>
+        <v>0.128</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="L2">
-        <v>0.3749208359721343</v>
+        <v>0.3657320872274143</v>
       </c>
       <c r="M2">
-        <v>36.1</v>
+        <v>39.4</v>
       </c>
       <c r="N2">
-        <v>0.0448558648111332</v>
+        <v>0.05877965090258094</v>
       </c>
       <c r="O2">
-        <v>0.6097972972972973</v>
+        <v>0.6712095400340715</v>
       </c>
       <c r="P2">
-        <v>36.1</v>
+        <v>39.4</v>
       </c>
       <c r="Q2">
-        <v>0.0448558648111332</v>
+        <v>0.05877965090258094</v>
       </c>
       <c r="R2">
-        <v>0.6097972972972973</v>
+        <v>0.6712095400340715</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>180.8</v>
+        <v>180.5</v>
       </c>
       <c r="V2">
-        <v>0.2246520874751491</v>
+        <v>0.2692824108608086</v>
       </c>
       <c r="W2">
-        <v>0.111320045129748</v>
+        <v>0.1166302404132724</v>
       </c>
       <c r="X2">
-        <v>0.1029808301471179</v>
+        <v>0.08691283085360388</v>
       </c>
       <c r="Y2">
-        <v>0.008339214982630141</v>
+        <v>0.02971740955966852</v>
       </c>
       <c r="Z2">
-        <v>0.1009074642126789</v>
+        <v>0.0878441245689891</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05694561925493129</v>
+        <v>0.04893308292506583</v>
       </c>
       <c r="AC2">
-        <v>-0.05694561925493129</v>
+        <v>-0.04893308292506583</v>
       </c>
       <c r="AD2">
-        <v>1618.6</v>
+        <v>1542.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1618.6</v>
+        <v>1542.7</v>
       </c>
       <c r="AG2">
-        <v>1437.8</v>
+        <v>1362.2</v>
       </c>
       <c r="AH2">
-        <v>0.6679045968474046</v>
+        <v>0.6971079981924989</v>
       </c>
       <c r="AI2">
-        <v>0.7628069183279136</v>
+        <v>0.7095157062042956</v>
       </c>
       <c r="AJ2">
-        <v>0.6411308302862748</v>
+        <v>0.6702091020910209</v>
       </c>
       <c r="AK2">
-        <v>0.7407140281283808</v>
+        <v>0.6832179757247466</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.102</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="E3">
-        <v>0.09359999999999999</v>
+        <v>0.0727</v>
       </c>
       <c r="F3">
-        <v>0.0429</v>
+        <v>0.128</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="L3">
-        <v>0.3749208359721343</v>
+        <v>0.3657320872274143</v>
       </c>
       <c r="M3">
-        <v>36.1</v>
+        <v>39.4</v>
       </c>
       <c r="N3">
-        <v>0.0448558648111332</v>
+        <v>0.05877965090258094</v>
       </c>
       <c r="O3">
-        <v>0.6097972972972973</v>
+        <v>0.6712095400340715</v>
       </c>
       <c r="P3">
-        <v>36.1</v>
+        <v>39.4</v>
       </c>
       <c r="Q3">
-        <v>0.0448558648111332</v>
+        <v>0.05877965090258094</v>
       </c>
       <c r="R3">
-        <v>0.6097972972972973</v>
+        <v>0.6712095400340715</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>180.8</v>
+        <v>180.5</v>
       </c>
       <c r="V3">
-        <v>0.2246520874751491</v>
+        <v>0.2692824108608086</v>
       </c>
       <c r="W3">
-        <v>0.111320045129748</v>
+        <v>0.1166302404132724</v>
       </c>
       <c r="X3">
-        <v>0.1029808301471179</v>
+        <v>0.08691283085360388</v>
       </c>
       <c r="Y3">
-        <v>0.008339214982630141</v>
+        <v>0.02971740955966852</v>
       </c>
       <c r="Z3">
-        <v>0.1009074642126789</v>
+        <v>0.0878441245689891</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05694561925493129</v>
+        <v>0.04893308292506583</v>
       </c>
       <c r="AC3">
-        <v>-0.05694561925493129</v>
+        <v>-0.04893308292506583</v>
       </c>
       <c r="AD3">
-        <v>1618.6</v>
+        <v>1542.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1618.6</v>
+        <v>1542.7</v>
       </c>
       <c r="AG3">
-        <v>1437.8</v>
+        <v>1362.2</v>
       </c>
       <c r="AH3">
-        <v>0.6679045968474046</v>
+        <v>0.6971079981924989</v>
       </c>
       <c r="AI3">
-        <v>0.7628069183279136</v>
+        <v>0.7095157062042956</v>
       </c>
       <c r="AJ3">
-        <v>0.6411308302862748</v>
+        <v>0.6702091020910209</v>
       </c>
       <c r="AK3">
-        <v>0.7407140281283808</v>
+        <v>0.6832179757247466</v>
       </c>
       <c r="AL3">
         <v>0</v>
